--- a/output/graficos_regionales/plot_regional_serie_i_ingr_mean_m_2019_nuble.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_mean_m_2019_nuble.xlsx
@@ -288,7 +288,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:49</t>
+    <t xml:space="preserve">2026-10-05 02:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -704,7 +704,7 @@
         <v>201340.23</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>307926.12</v>
+        <v>307926.13</v>
       </c>
     </row>
     <row r="3">
@@ -847,7 +847,7 @@
         <v>212440.92</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>324105.12</v>
+        <v>324105.13</v>
       </c>
     </row>
     <row r="16">
@@ -855,7 +855,7 @@
         <v>17</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>216091.12</v>
+        <v>216091.13</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>334453.53</v>
@@ -913,7 +913,7 @@
         <v>210483.27</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>329863.62</v>
+        <v>329863.63</v>
       </c>
     </row>
     <row r="22">
@@ -1251,7 +1251,7 @@
         <v>53</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>266206.12</v>
+        <v>266206.13</v>
       </c>
       <c r="C52" s="2" t="n">
         <v>387033.84</v>
@@ -1287,7 +1287,7 @@
         <v>267857.31</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>391178.62</v>
+        <v>391178.63</v>
       </c>
     </row>
     <row r="56">
@@ -1372,7 +1372,7 @@
         <v>64</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>291593.62</v>
+        <v>291593.63</v>
       </c>
       <c r="C63" s="2" t="n">
         <v>422267.97</v>
@@ -1515,7 +1515,7 @@
         <v>77</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>301779.12</v>
+        <v>301779.13</v>
       </c>
       <c r="C76" s="2" t="n">
         <v>440548.41</v>
@@ -1529,7 +1529,7 @@
         <v>305033.81</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>440497.12</v>
+        <v>440497.13</v>
       </c>
     </row>
     <row r="78">
@@ -1595,7 +1595,7 @@
         <v>312942.75</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>451935.62</v>
+        <v>451935.63</v>
       </c>
     </row>
     <row r="84">
@@ -1614,7 +1614,7 @@
         <v>86</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>355980.12</v>
+        <v>355980.13</v>
       </c>
       <c r="C85" s="2" t="n">
         <v>497221.19</v>
